--- a/data/trans_orig/IP11D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Habitat-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113835</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134149</t>
+          <t>134824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139877</t>
+          <t>139865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250321</t>
+          <t>250471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256435</t>
+          <t>256616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185174</t>
+          <t>185149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241206</t>
+          <t>243196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>253046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431359</t>
+          <t>431345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442394</t>
+          <t>442443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185095</t>
+          <t>185778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178521</t>
+          <t>178217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367255</t>
+          <t>366702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374098</t>
+          <t>374129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161954</t>
+          <t>161895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167379</t>
+          <t>167380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174959</t>
+          <t>175604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340709</t>
+          <t>340764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347892</t>
+          <t>347909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,47 +2152,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>9123</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>24445</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>15080</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>9056</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>24495</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>654846</t>
+          <t>654836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>662819</t>
+          <t>662467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742766</t>
+          <t>743236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756143</t>
+          <t>756256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1401508</t>
+          <t>1401558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1416947</t>
+          <t>1416880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP11D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3670</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5588</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124255</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>121236</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125509</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>116231</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>113610</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>119967</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>117305</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>121071</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>138337</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>134824</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>139865</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>362</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>254569</t>
+          <t>244223</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250471</t>
+          <t>240914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256616</t>
+          <t>245960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4889</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10914</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>232966</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>226846</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>235584</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>188704</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>185149</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>190128</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>182728</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179174</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184063</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250307</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>243196</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253046</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>615</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>439011</t>
+          <t>415694</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431345</t>
+          <t>408646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442443</t>
+          <t>418427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236247</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236247</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236247</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190128</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190128</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190128</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254110</t>
+          <t>184063</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254110</t>
+          <t>184063</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254110</t>
+          <t>184063</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444238</t>
+          <t>420311</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444238</t>
+          <t>420311</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444238</t>
+          <t>420311</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5828</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3807</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4366</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7069</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166452</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162513</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>188797</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>185778</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>155344</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151838</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>156204</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>183264</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>178217</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>185286</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>448</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>372060</t>
+          <t>321796</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366702</t>
+          <t>316890</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374129</t>
+          <t>323690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6067</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167562</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162976</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>165829</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161895</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167380</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>179452</t>
+          <t>164989</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175604</t>
+          <t>160914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>345282</t>
+          <t>332552</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340764</t>
+          <t>327457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347909</t>
+          <t>335001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8635</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16081</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10120</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>691235</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683789</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>695476</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>659562</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>654836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>662467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>751360</t>
+          <t>623030</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743236</t>
+          <t>617765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756256</t>
+          <t>626065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1410923</t>
+          <t>1314265</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1401558</t>
+          <t>1305083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1416880</t>
+          <t>1319314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
